--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -66,12 +66,12 @@
     <t xml:space="preserve">La Pintana</t>
   </si>
   <si>
+    <t xml:space="preserve">Talagante</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cerro Navia</t>
   </si>
   <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
@@ -81,12 +81,12 @@
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:33</t>
+    <t xml:space="preserve">2026-09-09 23:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -801,7 +801,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>13103</v>
+        <v>13601</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2020</v>
@@ -818,7 +818,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>13601</v>
+        <v>13103</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2020</v>
@@ -886,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13106</v>
+        <v>13126</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2020</v>
@@ -903,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13126</v>
+        <v>13106</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2020</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:31</t>
+    <t xml:space="preserve">2026-09-17 14:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -66,27 +66,27 @@
     <t xml:space="preserve">La Pintana</t>
   </si>
   <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talagante</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Calera de Tango</t>
   </si>
   <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Ramón</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+    <t xml:space="preserve">Estación Central</t>
   </si>
   <si>
     <t xml:space="preserve">Quinta Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">Estación Central</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pirque</t>
   </si>
   <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
     <t xml:space="preserve">El Bosque</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:25</t>
+    <t xml:space="preserve">2026-09-23 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -801,7 +801,7 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>13601</v>
+        <v>13103</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2020</v>
@@ -818,7 +818,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>13103</v>
+        <v>13601</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2020</v>
@@ -852,7 +852,7 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>13131</v>
+        <v>13121</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2020</v>
@@ -869,7 +869,7 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>13121</v>
+        <v>13131</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2020</v>
@@ -886,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>13126</v>
+        <v>13106</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2020</v>
@@ -903,7 +903,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>13106</v>
+        <v>13126</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2020</v>
@@ -971,7 +971,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>13202</v>
+        <v>13111</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2020</v>
@@ -988,7 +988,7 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>13111</v>
+        <v>13202</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2020</v>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13505</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2020</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:53</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1582,7 +1579,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-02 11:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:25</t>
+    <t xml:space="preserve">2026-10-02 14:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2020_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:59</t>
+    <t xml:space="preserve">2026-10-05 12:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
